--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4056A4F3-E308-4AD9-9C6D-9E2BE73BF60B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7CF05B-6957-469B-9ECA-F9FC81381CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="906" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,8 @@
     <sheet name="String_ScenarioTalk" sheetId="5" r:id="rId7"/>
     <sheet name="String_Story" sheetId="8" r:id="rId8"/>
     <sheet name="String_GuideQuest" sheetId="9" r:id="rId9"/>
-    <sheet name="String_Traits" sheetId="10" r:id="rId10"/>
+    <sheet name="String_Quest" sheetId="12" r:id="rId10"/>
+    <sheet name="String_Traits" sheetId="10" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1986" uniqueCount="1068">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2038" uniqueCount="1101">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4206,6 +4207,117 @@
   </si>
   <si>
     <t>기타</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CATEGORY_NAME_DAILY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CATEGORY_NAME_WEEKLY</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일일 임무</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주간 임무</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUTTON_RECEIVE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>받기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUTTON_NAVIGATION</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUTTON_READ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>login</t>
+  </si>
+  <si>
+    <t>enemy_kill</t>
+  </si>
+  <si>
+    <t>tournament_play</t>
+  </si>
+  <si>
+    <t>raid_play</t>
+  </si>
+  <si>
+    <t>gacha_proceed</t>
+  </si>
+  <si>
+    <t>rice_claim</t>
+  </si>
+  <si>
+    <t>gole_claim</t>
+  </si>
+  <si>
+    <t>office_dispatch</t>
+  </si>
+  <si>
+    <t>daily_dungeon_play</t>
+  </si>
+  <si>
+    <t>stage_boss_kill</t>
+  </si>
+  <si>
+    <t>ads_watch</t>
+  </si>
+  <si>
+    <t>item_buy</t>
+  </si>
+  <si>
+    <t>item_use</t>
+  </si>
+  <si>
+    <t>로그인</t>
+  </si>
+  <si>
+    <t>연회 진행하기</t>
+  </si>
+  <si>
+    <t>관아 파견하기</t>
+  </si>
+  <si>
+    <t>요일 던전 플레이하기</t>
+  </si>
+  <si>
+    <t>스테이지 보스 처치하기</t>
+  </si>
+  <si>
+    <t>광고 시청하기</t>
+  </si>
+  <si>
+    <t>상품 구매하기</t>
+  </si>
+  <si>
+    <t>아이템 사용하기</t>
+  </si>
+  <si>
+    <t>STATUS_COMPLETE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4438,7 +4550,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4639,6 +4751,21 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4989,6 +5116,1081 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A30C963D-31D9-4CED-9D49-CF56C311BF1E}">
+  <dimension ref="A1:G126"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.875" style="51" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.875" style="54" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.625" style="55" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="41.375" style="55" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="65.75" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="51"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="D1" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="F1" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="31" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="40" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="37" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="21"/>
+      <c r="B3" s="49"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="20" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E3" s="69" t="s">
+        <v>1070</v>
+      </c>
+      <c r="F3" s="43"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="21"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="20" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E4" s="69" t="s">
+        <v>1071</v>
+      </c>
+      <c r="F4" s="43"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="21"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="58" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D5" s="20" t="str">
+        <f t="shared" ref="D5:D16" si="0">UPPER(C5)&amp;"_NAME"</f>
+        <v>LOGIN_NAME</v>
+      </c>
+      <c r="E5" s="70" t="s">
+        <v>1090</v>
+      </c>
+      <c r="F5" s="43"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="21"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="58" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D6" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>ENEMY_KILL_NAME</v>
+      </c>
+      <c r="E6" s="70" t="s">
+        <v>862</v>
+      </c>
+      <c r="F6" s="43"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="21"/>
+      <c r="B7" s="52"/>
+      <c r="C7" s="58" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D7" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>TOURNAMENT_PLAY_NAME</v>
+      </c>
+      <c r="E7" s="70" t="s">
+        <v>863</v>
+      </c>
+      <c r="F7" s="43"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="21"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="58" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D8" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>RAID_PLAY_NAME</v>
+      </c>
+      <c r="E8" s="70" t="s">
+        <v>864</v>
+      </c>
+      <c r="F8" s="43"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="21"/>
+      <c r="B9" s="52"/>
+      <c r="C9" s="58" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D9" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>GACHA_PROCEED_NAME</v>
+      </c>
+      <c r="E9" s="70" t="s">
+        <v>1091</v>
+      </c>
+      <c r="F9" s="43"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="21"/>
+      <c r="B10" s="49"/>
+      <c r="C10" s="58" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D10" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>RICE_CLAIM_NAME</v>
+      </c>
+      <c r="E10" s="70" t="s">
+        <v>866</v>
+      </c>
+      <c r="F10" s="43"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="21"/>
+      <c r="B11" s="49"/>
+      <c r="C11" s="58" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D11" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>GOLE_CLAIM_NAME</v>
+      </c>
+      <c r="E11" s="70" t="s">
+        <v>867</v>
+      </c>
+      <c r="F11" s="43"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="21"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="58" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D12" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>OFFICE_DISPATCH_NAME</v>
+      </c>
+      <c r="E12" s="70" t="s">
+        <v>1092</v>
+      </c>
+      <c r="F12" s="43"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="21"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="58" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D13" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>DAILY_DUNGEON_PLAY_NAME</v>
+      </c>
+      <c r="E13" s="70" t="s">
+        <v>1093</v>
+      </c>
+      <c r="F13" s="43"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="21"/>
+      <c r="B14" s="49"/>
+      <c r="C14" s="58" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D14" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>STAGE_BOSS_KILL_NAME</v>
+      </c>
+      <c r="E14" s="70" t="s">
+        <v>1094</v>
+      </c>
+      <c r="F14" s="43"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="21"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="58" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D15" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>ADS_WATCH_NAME</v>
+      </c>
+      <c r="E15" s="70" t="s">
+        <v>1095</v>
+      </c>
+      <c r="F15" s="43"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="21"/>
+      <c r="B16" s="49"/>
+      <c r="C16" s="58" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D16" s="20" t="str">
+        <f t="shared" si="0"/>
+        <v>ITEM_BUY_NAME</v>
+      </c>
+      <c r="E16" s="70" t="s">
+        <v>1096</v>
+      </c>
+      <c r="F16" s="43"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="21"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="58" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D17" s="20" t="str">
+        <f>UPPER(C17)&amp;"_NAME"</f>
+        <v>ITEM_USE_NAME</v>
+      </c>
+      <c r="E17" s="70" t="s">
+        <v>1097</v>
+      </c>
+      <c r="F17" s="43"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="21"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="20" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E18" s="70" t="s">
+        <v>1099</v>
+      </c>
+      <c r="F18" s="43"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="21"/>
+      <c r="B19" s="49"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="20"/>
+      <c r="F19" s="43"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="21"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="41"/>
+      <c r="F20" s="43"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="21"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="41"/>
+      <c r="F21" s="43"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="21"/>
+      <c r="B22" s="49"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="41"/>
+      <c r="F22" s="43"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="21"/>
+      <c r="B23" s="49"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="41"/>
+      <c r="F23" s="43"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="21"/>
+      <c r="B24" s="49"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="41"/>
+      <c r="F24" s="43"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="21"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="41"/>
+      <c r="F25" s="43"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="21"/>
+      <c r="B26" s="49"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="41"/>
+      <c r="F26" s="43"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="21"/>
+      <c r="B27" s="49"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="41"/>
+      <c r="F27" s="43"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="21"/>
+      <c r="B28" s="49"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="41"/>
+      <c r="F28" s="43"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="21"/>
+      <c r="B29" s="49"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="41"/>
+      <c r="F29" s="43"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="21"/>
+      <c r="B30" s="49"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="41"/>
+      <c r="F30" s="43"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="21"/>
+      <c r="B31" s="49"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="41"/>
+      <c r="F31" s="43"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="21"/>
+      <c r="B32" s="49"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="41"/>
+      <c r="F32" s="43"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="21"/>
+      <c r="B33" s="49"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="41"/>
+      <c r="F33" s="43"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="21"/>
+      <c r="B34" s="49"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="41"/>
+      <c r="F34" s="43"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="21"/>
+      <c r="B35" s="50"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="42"/>
+      <c r="F35" s="44"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="21"/>
+      <c r="B36" s="49"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="41"/>
+      <c r="F36" s="43"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="21"/>
+      <c r="B37" s="49"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="41"/>
+      <c r="F37" s="45"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="21"/>
+      <c r="B38" s="49"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="41"/>
+      <c r="F38" s="43"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="21"/>
+      <c r="B39" s="49"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="41"/>
+      <c r="F39" s="43"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="21"/>
+      <c r="B40" s="49"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="41"/>
+      <c r="E40" s="71"/>
+      <c r="F40" s="43"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="21"/>
+      <c r="B41" s="49"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="71"/>
+      <c r="F41" s="43"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="21"/>
+      <c r="B42" s="49"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="41"/>
+      <c r="F42" s="43"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="21"/>
+      <c r="B43" s="49"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="41"/>
+      <c r="E43" s="71"/>
+      <c r="F43" s="43"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="21"/>
+      <c r="B44" s="49"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="41"/>
+      <c r="F44" s="43"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="21"/>
+      <c r="B45" s="49"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="41"/>
+      <c r="F45" s="43"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="21"/>
+      <c r="B46" s="49"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="41"/>
+      <c r="F46" s="43"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="21"/>
+      <c r="B47" s="49"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="41"/>
+      <c r="F47" s="43"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="21"/>
+      <c r="B48" s="49"/>
+      <c r="C48" s="19"/>
+      <c r="D48" s="41"/>
+      <c r="F48" s="43"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" s="21"/>
+      <c r="B49" s="49"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="41"/>
+      <c r="F49" s="43"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="21"/>
+      <c r="B50" s="49"/>
+      <c r="C50" s="19"/>
+      <c r="D50" s="41"/>
+      <c r="F50" s="43"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="21"/>
+      <c r="B51" s="49"/>
+      <c r="C51" s="19"/>
+      <c r="D51" s="41"/>
+      <c r="F51" s="43"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="21"/>
+      <c r="B52" s="49"/>
+      <c r="C52" s="19"/>
+      <c r="D52" s="41"/>
+      <c r="F52" s="43"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="21"/>
+      <c r="B53" s="49"/>
+      <c r="C53" s="19"/>
+      <c r="D53" s="41"/>
+      <c r="F53" s="43"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A54" s="21"/>
+      <c r="B54" s="49"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="41"/>
+      <c r="F54" s="43"/>
+      <c r="G54" s="35"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55" s="21"/>
+      <c r="B55" s="49"/>
+      <c r="C55" s="19"/>
+      <c r="D55" s="41"/>
+      <c r="F55" s="43"/>
+      <c r="G55" s="35"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56" s="21"/>
+      <c r="B56" s="49"/>
+      <c r="C56" s="19"/>
+      <c r="D56" s="41"/>
+      <c r="F56" s="43"/>
+      <c r="G56" s="35"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" s="21"/>
+      <c r="B57" s="49"/>
+      <c r="C57" s="19"/>
+      <c r="D57" s="41"/>
+      <c r="F57" s="43"/>
+      <c r="G57" s="35"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" s="21"/>
+      <c r="B58" s="49"/>
+      <c r="C58" s="19"/>
+      <c r="D58" s="41"/>
+      <c r="F58" s="43"/>
+      <c r="G58" s="35"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" s="21"/>
+      <c r="B59" s="49"/>
+      <c r="C59" s="19"/>
+      <c r="D59" s="41"/>
+      <c r="F59" s="43"/>
+      <c r="G59" s="35"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60" s="21"/>
+      <c r="B60" s="49"/>
+      <c r="C60" s="19"/>
+      <c r="D60" s="41"/>
+      <c r="F60" s="43"/>
+      <c r="G60" s="35"/>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" s="21"/>
+      <c r="B61" s="49"/>
+      <c r="C61" s="19"/>
+      <c r="D61" s="41"/>
+      <c r="F61" s="43"/>
+      <c r="G61" s="35"/>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" s="21"/>
+      <c r="B62" s="49"/>
+      <c r="C62" s="19"/>
+      <c r="D62" s="41"/>
+      <c r="F62" s="43"/>
+      <c r="G62" s="35"/>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" s="21"/>
+      <c r="B63" s="49"/>
+      <c r="C63" s="19"/>
+      <c r="D63" s="41"/>
+      <c r="F63" s="43"/>
+      <c r="G63" s="35"/>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" s="21"/>
+      <c r="B64" s="49"/>
+      <c r="C64" s="19"/>
+      <c r="D64" s="41"/>
+      <c r="F64" s="43"/>
+      <c r="G64" s="35"/>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" s="21"/>
+      <c r="B65" s="49"/>
+      <c r="C65" s="19"/>
+      <c r="D65" s="41"/>
+      <c r="F65" s="43"/>
+      <c r="G65" s="35"/>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A66" s="21"/>
+      <c r="B66" s="49"/>
+      <c r="C66" s="19"/>
+      <c r="D66" s="41"/>
+      <c r="F66" s="43"/>
+      <c r="G66" s="35"/>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A67" s="21"/>
+      <c r="B67" s="49"/>
+      <c r="C67" s="19"/>
+      <c r="D67" s="41"/>
+      <c r="F67" s="43"/>
+      <c r="G67" s="35"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68" s="21"/>
+      <c r="B68" s="49"/>
+      <c r="C68" s="19"/>
+      <c r="D68" s="41"/>
+      <c r="F68" s="43"/>
+      <c r="G68" s="35"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69" s="21"/>
+      <c r="B69" s="49"/>
+      <c r="C69" s="19"/>
+      <c r="D69" s="41"/>
+      <c r="F69" s="43"/>
+      <c r="G69" s="35"/>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70" s="21"/>
+      <c r="B70" s="49"/>
+      <c r="C70" s="19"/>
+      <c r="D70" s="41"/>
+      <c r="F70" s="43"/>
+      <c r="G70" s="35"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A71" s="21"/>
+      <c r="B71" s="49"/>
+      <c r="C71" s="19"/>
+      <c r="D71" s="41"/>
+      <c r="F71" s="43"/>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72" s="21"/>
+      <c r="B72" s="49"/>
+      <c r="C72" s="19"/>
+      <c r="D72" s="41"/>
+      <c r="F72" s="43"/>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73" s="21"/>
+      <c r="B73" s="50"/>
+      <c r="C73" s="22"/>
+      <c r="D73" s="41"/>
+      <c r="F73" s="44"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" s="21"/>
+      <c r="B74" s="49"/>
+      <c r="C74" s="19"/>
+      <c r="D74" s="41"/>
+      <c r="F74" s="43"/>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A75" s="21"/>
+      <c r="B75" s="49"/>
+      <c r="C75" s="19"/>
+      <c r="D75" s="41"/>
+      <c r="F75" s="45"/>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76" s="21"/>
+      <c r="B76" s="49"/>
+      <c r="C76" s="22"/>
+      <c r="D76" s="41"/>
+      <c r="F76" s="44"/>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A77" s="21"/>
+      <c r="B77" s="49"/>
+      <c r="C77" s="19"/>
+      <c r="D77" s="41"/>
+      <c r="F77" s="43"/>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A78" s="21"/>
+      <c r="B78" s="49"/>
+      <c r="C78" s="19"/>
+      <c r="D78" s="41"/>
+      <c r="F78" s="43"/>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A79" s="21"/>
+      <c r="B79" s="25"/>
+      <c r="C79" s="26"/>
+      <c r="D79" s="41"/>
+      <c r="F79" s="43"/>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A80" s="21"/>
+      <c r="B80" s="25"/>
+      <c r="C80" s="26"/>
+      <c r="D80" s="41"/>
+      <c r="F80" s="43"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A81" s="21"/>
+      <c r="B81" s="25"/>
+      <c r="C81" s="26"/>
+      <c r="D81" s="41"/>
+      <c r="F81" s="43"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A82" s="21"/>
+      <c r="B82" s="25"/>
+      <c r="C82" s="26"/>
+      <c r="D82" s="41"/>
+      <c r="F82" s="43"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A83" s="21"/>
+      <c r="B83" s="25"/>
+      <c r="C83" s="26"/>
+      <c r="D83" s="41"/>
+      <c r="F83" s="43"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A84" s="21"/>
+      <c r="B84" s="25"/>
+      <c r="C84" s="26"/>
+      <c r="D84" s="41"/>
+      <c r="F84" s="43"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A85" s="21"/>
+      <c r="B85" s="25"/>
+      <c r="C85" s="26"/>
+      <c r="D85" s="41"/>
+      <c r="F85" s="43"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A86" s="21"/>
+      <c r="B86" s="25"/>
+      <c r="C86" s="26"/>
+      <c r="D86" s="41"/>
+      <c r="F86" s="43"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A87" s="21"/>
+      <c r="B87" s="25"/>
+      <c r="C87" s="26"/>
+      <c r="D87" s="41"/>
+      <c r="F87" s="43"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A88" s="21"/>
+      <c r="B88" s="25"/>
+      <c r="C88" s="26"/>
+      <c r="D88" s="41"/>
+      <c r="F88" s="43"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A89" s="21"/>
+      <c r="B89" s="25"/>
+      <c r="C89" s="26"/>
+      <c r="D89" s="41"/>
+      <c r="F89" s="43"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A90" s="21"/>
+      <c r="B90" s="25"/>
+      <c r="C90" s="26"/>
+      <c r="D90" s="41"/>
+      <c r="F90" s="43"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A91" s="21"/>
+      <c r="B91" s="25"/>
+      <c r="C91" s="26"/>
+      <c r="D91" s="41"/>
+      <c r="F91" s="43"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A92" s="21"/>
+      <c r="B92" s="25"/>
+      <c r="C92" s="26"/>
+      <c r="D92" s="41"/>
+      <c r="F92" s="43"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A93" s="21"/>
+      <c r="B93" s="25"/>
+      <c r="C93" s="26"/>
+      <c r="D93" s="41"/>
+      <c r="F93" s="43"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A94" s="21"/>
+      <c r="B94" s="25"/>
+      <c r="C94" s="26"/>
+      <c r="D94" s="41"/>
+      <c r="F94" s="43"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A95" s="21"/>
+      <c r="B95" s="25"/>
+      <c r="C95" s="26"/>
+      <c r="D95" s="41"/>
+      <c r="E95" s="72"/>
+      <c r="F95" s="43"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A96" s="21"/>
+      <c r="B96" s="25"/>
+      <c r="C96" s="26"/>
+      <c r="D96" s="41"/>
+      <c r="E96" s="72"/>
+      <c r="F96" s="43"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A97" s="21"/>
+      <c r="B97" s="25"/>
+      <c r="C97" s="26"/>
+      <c r="D97" s="41"/>
+      <c r="F97" s="43"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A98" s="21"/>
+      <c r="B98" s="25"/>
+      <c r="C98" s="26"/>
+      <c r="D98" s="41"/>
+      <c r="F98" s="43"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A99" s="21"/>
+      <c r="B99" s="25"/>
+      <c r="C99" s="26"/>
+      <c r="D99" s="41"/>
+      <c r="F99" s="43"/>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A100" s="21"/>
+      <c r="B100" s="25"/>
+      <c r="C100" s="26"/>
+      <c r="D100" s="41"/>
+      <c r="F100" s="43"/>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A101" s="21"/>
+      <c r="B101" s="25"/>
+      <c r="C101" s="26"/>
+      <c r="D101" s="41"/>
+      <c r="F101" s="43"/>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A102" s="21"/>
+      <c r="B102" s="25"/>
+      <c r="C102" s="26"/>
+      <c r="D102" s="41"/>
+      <c r="F102" s="43"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A103" s="21"/>
+      <c r="B103" s="25"/>
+      <c r="C103" s="26"/>
+      <c r="D103" s="41"/>
+      <c r="F103" s="43"/>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A104" s="21"/>
+      <c r="B104" s="25"/>
+      <c r="C104" s="26"/>
+      <c r="D104" s="41"/>
+      <c r="F104" s="43"/>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A105" s="21"/>
+      <c r="B105" s="25"/>
+      <c r="C105" s="26"/>
+      <c r="D105" s="41"/>
+      <c r="F105" s="43"/>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A106" s="21"/>
+      <c r="B106" s="25"/>
+      <c r="C106" s="26"/>
+      <c r="D106" s="41"/>
+      <c r="F106" s="43"/>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A107" s="21"/>
+      <c r="B107" s="25"/>
+      <c r="C107" s="26"/>
+      <c r="D107" s="41"/>
+      <c r="F107" s="43"/>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A108" s="21"/>
+      <c r="B108" s="25"/>
+      <c r="C108" s="26"/>
+      <c r="D108" s="41"/>
+      <c r="F108" s="43"/>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A109" s="21"/>
+      <c r="B109" s="25"/>
+      <c r="C109" s="26"/>
+      <c r="D109" s="41"/>
+      <c r="F109" s="43"/>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A110" s="21"/>
+      <c r="B110" s="25"/>
+      <c r="C110" s="26"/>
+      <c r="D110" s="41"/>
+      <c r="F110" s="43"/>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A111" s="21"/>
+      <c r="B111" s="25"/>
+      <c r="C111" s="26"/>
+      <c r="D111" s="41"/>
+      <c r="F111" s="43"/>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A112" s="21"/>
+      <c r="B112" s="25"/>
+      <c r="C112" s="26"/>
+      <c r="D112" s="41"/>
+      <c r="F112" s="43"/>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A113" s="21"/>
+      <c r="B113" s="25"/>
+      <c r="C113" s="26"/>
+      <c r="D113" s="41"/>
+      <c r="F113" s="43"/>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A114" s="21"/>
+      <c r="B114" s="25"/>
+      <c r="C114" s="26"/>
+      <c r="D114" s="41"/>
+      <c r="F114" s="43"/>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A115" s="21"/>
+      <c r="B115" s="25"/>
+      <c r="C115" s="26"/>
+      <c r="D115" s="41"/>
+      <c r="F115" s="43"/>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A116" s="21"/>
+      <c r="B116" s="25"/>
+      <c r="C116" s="26"/>
+      <c r="D116" s="41"/>
+      <c r="F116" s="43"/>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A117" s="21"/>
+      <c r="B117" s="25"/>
+      <c r="C117" s="26"/>
+      <c r="D117" s="41"/>
+      <c r="F117" s="43"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A118" s="21"/>
+      <c r="B118" s="25"/>
+      <c r="C118" s="26"/>
+      <c r="D118" s="41"/>
+      <c r="F118" s="43"/>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A119" s="21"/>
+      <c r="B119" s="25"/>
+      <c r="C119" s="26"/>
+      <c r="D119" s="41"/>
+      <c r="F119" s="43"/>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A120" s="21"/>
+      <c r="B120" s="25"/>
+      <c r="C120" s="26"/>
+      <c r="D120" s="41"/>
+      <c r="F120" s="43"/>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A121" s="21"/>
+      <c r="B121" s="25"/>
+      <c r="C121" s="26"/>
+      <c r="D121" s="41"/>
+      <c r="F121" s="43"/>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A122" s="21"/>
+      <c r="B122" s="25"/>
+      <c r="C122" s="26"/>
+      <c r="D122" s="41"/>
+      <c r="F122" s="43"/>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A123" s="21"/>
+      <c r="B123" s="25"/>
+      <c r="C123" s="26"/>
+      <c r="D123" s="41"/>
+      <c r="F123" s="43"/>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A124" s="21"/>
+      <c r="B124" s="25"/>
+      <c r="C124" s="26"/>
+      <c r="D124" s="41"/>
+      <c r="F124" s="43"/>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A125" s="21"/>
+      <c r="B125" s="25"/>
+      <c r="C125" s="26"/>
+      <c r="D125" s="41"/>
+      <c r="F125" s="43"/>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A126" s="21"/>
+      <c r="B126" s="25"/>
+      <c r="C126" s="26"/>
+      <c r="D126" s="41"/>
+      <c r="F126" s="43"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7059F2B8-C8CA-4434-8401-F4979C2748FC}">
   <dimension ref="A1:E52"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -5732,7 +6934,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:D104"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="44.375" bestFit="1" customWidth="1"/>
@@ -6821,6 +8023,30 @@
       </c>
       <c r="C101" s="27" t="s">
         <v>999</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B102" s="6" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B103" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C103" s="68" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B104" s="6" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C104" s="68" t="s">
+        <v>1076</v>
       </c>
     </row>
   </sheetData>
@@ -6902,7 +8128,7 @@
         <v>1001</v>
       </c>
       <c r="B5" s="17" t="str">
-        <f t="shared" ref="B5:B12" si="0">"CATEGORY_"&amp;UPPER(A5)</f>
+        <f t="shared" ref="B5:B10" si="0">"CATEGORY_"&amp;UPPER(A5)</f>
         <v>CATEGORY_SOUL_STONE</v>
       </c>
       <c r="C5" s="66" t="s">

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7CF05B-6957-469B-9ECA-F9FC81381CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B79E77-DF2E-418A-9810-8391AB67E2D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="906" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2038" uniqueCount="1101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2042" uniqueCount="1104">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4318,6 +4318,18 @@
   </si>
   <si>
     <t>이동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>COMPLETE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>COMPLETE_REWARD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>획득완료</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4550,7 +4562,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4767,6 +4779,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6934,7 +6949,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D104"/>
+  <dimension ref="A1:D106"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="44.375" bestFit="1" customWidth="1"/>
@@ -8047,6 +8062,22 @@
       </c>
       <c r="C104" s="68" t="s">
         <v>1076</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B105" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C105" s="68" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B106" s="73" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C106" s="68" t="s">
+        <v>1103</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelToJSONConverter/excel/stringTable.xlsx
+++ b/ExcelToJSONConverter/excel/stringTable.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B79E77-DF2E-418A-9810-8391AB67E2D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F28EE9A-FA80-4DB8-8873-ACCA9DA7108F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="906" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="1395" windowWidth="29040" windowHeight="16440" tabRatio="906" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2042" uniqueCount="1104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2050" uniqueCount="1111">
   <si>
     <t>kr</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4330,6 +4330,34 @@
   </si>
   <si>
     <t>획득완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>편집</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>확인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUTTON_EDIT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUTTON_CONFIRM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUTTON_SAVE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BUTTON_COMPLETE</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -6949,7 +6977,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D106"/>
+  <dimension ref="A1:D110"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="44.375" bestFit="1" customWidth="1"/>
@@ -8078,6 +8106,38 @@
       </c>
       <c r="C106" s="68" t="s">
         <v>1103</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B107" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C107" s="68" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B108" s="73" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C108" s="68" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B109" t="s">
+        <v>1109</v>
+      </c>
+      <c r="C109" s="68" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B110" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C110" s="68" t="s">
+        <v>1099</v>
       </c>
     </row>
   </sheetData>
